--- a/Thermo/Solutions/solution_models_PFM.xlsx
+++ b/Thermo/Solutions/solution_models_PFM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\Thermo\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63A7550-F47E-44CB-8539-8E060BF7E87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC96035-AC31-49B4-9506-930DADB712C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="20" activeTab="28" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="23" activeTab="24" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Melt (Ab-An)" sheetId="50" r:id="rId1"/>
@@ -6161,40 +6161,40 @@
         <v>205</v>
       </c>
       <c r="B19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="C19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="I19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="J19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="K19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="L19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="M19">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -8606,25 +8606,25 @@
         <v>205</v>
       </c>
       <c r="B16">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C16">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D16">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E16">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F16">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G16">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="H16">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -10725,43 +10725,43 @@
         <v>205</v>
       </c>
       <c r="B20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="C20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="D20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="J20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="L20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="M20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="N20">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -15024,34 +15024,34 @@
         <v>205</v>
       </c>
       <c r="B17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="C17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="I17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="J17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="K17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -33173,19 +33173,19 @@
         <v>205</v>
       </c>
       <c r="B12">
-        <v>6.7000000000000004E-2</v>
+        <v>0.02</v>
       </c>
       <c r="C12">
-        <v>6.7000000000000004E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D12">
-        <v>6.7000000000000004E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E12">
-        <v>6.7000000000000004E-2</v>
+        <v>0.02</v>
       </c>
       <c r="F12">
-        <v>6.7000000000000004E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">

--- a/Thermo/Solutions/solution_models_PFM.xlsx
+++ b/Thermo/Solutions/solution_models_PFM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\Thermo\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC96035-AC31-49B4-9506-930DADB712C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2794E5CB-7459-44C3-8080-47DE6FD43B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="23" activeTab="24" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="8" activeTab="10" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Melt (Ab-An)" sheetId="50" r:id="rId1"/>
@@ -2279,19 +2279,19 @@
         <v>205</v>
       </c>
       <c r="B14">
-        <v>6.7000000000000004E-2</v>
+        <v>0.02</v>
       </c>
       <c r="C14">
-        <v>6.7000000000000004E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D14">
-        <v>6.7000000000000004E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E14">
-        <v>6.7000000000000004E-2</v>
+        <v>0.02</v>
       </c>
       <c r="F14">
-        <v>6.7000000000000004E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -6161,40 +6161,40 @@
         <v>205</v>
       </c>
       <c r="B19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="M19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -8606,25 +8606,25 @@
         <v>205</v>
       </c>
       <c r="B16">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C16">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D16">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E16">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="F16">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G16">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="H16">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -10725,43 +10725,43 @@
         <v>205</v>
       </c>
       <c r="B20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="C20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="E20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="J20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="L20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="M20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="N20">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">

--- a/Thermo/Solutions/solution_models_PFM.xlsx
+++ b/Thermo/Solutions/solution_models_PFM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\Thermo\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2794E5CB-7459-44C3-8080-47DE6FD43B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5702E331-A572-4A37-8D94-09319BB33E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="8" activeTab="10" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="17" activeTab="26" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Melt (Ab-An)" sheetId="50" r:id="rId1"/>
@@ -2279,19 +2279,19 @@
         <v>205</v>
       </c>
       <c r="B14">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C14">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D14">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E14">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F14">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -8606,25 +8606,25 @@
         <v>205</v>
       </c>
       <c r="B16">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="C16">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D16">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E16">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="F16">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G16">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="H16">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -10708,7 +10708,7 @@
         <v>1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <v>0</v>

--- a/Thermo/Solutions/solution_models_PFM.xlsx
+++ b/Thermo/Solutions/solution_models_PFM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\Thermo\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5702E331-A572-4A37-8D94-09319BB33E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0021E9-8CA4-4161-A83E-E6E24F43396C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="17" activeTab="26" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
@@ -8606,25 +8606,25 @@
         <v>205</v>
       </c>
       <c r="B16">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C16">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D16">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E16">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F16">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G16">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H16">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -10725,43 +10725,43 @@
         <v>205</v>
       </c>
       <c r="B20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="K20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="L20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">

--- a/Thermo/Solutions/solution_models_PFM.xlsx
+++ b/Thermo/Solutions/solution_models_PFM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\Thermo\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0021E9-8CA4-4161-A83E-E6E24F43396C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FDA618-B5DC-4825-BB24-F000E01542E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="17" activeTab="26" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="8" activeTab="11" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Melt (Ab-An)" sheetId="50" r:id="rId1"/>
@@ -24,52 +24,53 @@
     <sheet name="Antigorite" sheetId="8" r:id="rId9"/>
     <sheet name="Talc" sheetId="10" r:id="rId10"/>
     <sheet name="Feldspar" sheetId="49" r:id="rId11"/>
-    <sheet name="Feldspar(I1)" sheetId="12" r:id="rId12"/>
-    <sheet name="Feldspar(C1)" sheetId="11" r:id="rId13"/>
-    <sheet name="Brucite" sheetId="9" r:id="rId14"/>
-    <sheet name="Olivine(example)" sheetId="38" r:id="rId15"/>
-    <sheet name="Olivine" sheetId="2" r:id="rId16"/>
-    <sheet name="Olivine_Ori" sheetId="57" r:id="rId17"/>
-    <sheet name="Ilmenite" sheetId="13" r:id="rId18"/>
-    <sheet name="Fluid-H2O" sheetId="48" r:id="rId19"/>
-    <sheet name="Fluid-CO2-H2O" sheetId="1" r:id="rId20"/>
-    <sheet name="Fluid-NaCl-H2O" sheetId="34" r:id="rId21"/>
-    <sheet name="Fluid-NaCl-CO2-H2O" sheetId="35" r:id="rId22"/>
-    <sheet name="Orthopyroxene" sheetId="5" r:id="rId23"/>
-    <sheet name="Orthopyroxene_Ori" sheetId="56" r:id="rId24"/>
-    <sheet name="Garnet" sheetId="6" r:id="rId25"/>
-    <sheet name="Garnet_Ori" sheetId="54" r:id="rId26"/>
-    <sheet name="Clinopyroxene" sheetId="7" r:id="rId27"/>
-    <sheet name="Clinopyroxene_Ori" sheetId="55" r:id="rId28"/>
-    <sheet name="Spinel" sheetId="14" r:id="rId29"/>
-    <sheet name="Fluid(H18)" sheetId="15" r:id="rId30"/>
-    <sheet name="Fluid(H18)-NaCl-CO2" sheetId="36" r:id="rId31"/>
-    <sheet name="Amphibole" sheetId="16" r:id="rId32"/>
-    <sheet name="Biotite" sheetId="17" r:id="rId33"/>
-    <sheet name="Muscovite" sheetId="18" r:id="rId34"/>
-    <sheet name="Epidote" sheetId="19" r:id="rId35"/>
-    <sheet name="Cordierite" sheetId="20" r:id="rId36"/>
-    <sheet name="Chlorite" sheetId="21" r:id="rId37"/>
-    <sheet name="Staurolite" sheetId="22" r:id="rId38"/>
-    <sheet name="Chloritoid" sheetId="23" r:id="rId39"/>
-    <sheet name="Magnesite" sheetId="31" r:id="rId40"/>
-    <sheet name="Dolomite" sheetId="32" r:id="rId41"/>
-    <sheet name="Akimotoite" sheetId="24" r:id="rId42"/>
-    <sheet name="Corundum" sheetId="25" r:id="rId43"/>
-    <sheet name="Corundum_Ori" sheetId="58" r:id="rId44"/>
-    <sheet name="Perovskite" sheetId="26" r:id="rId45"/>
-    <sheet name="Ringwoodite" sheetId="27" r:id="rId46"/>
-    <sheet name="Wadsleyite" sheetId="28" r:id="rId47"/>
-    <sheet name="Majorite" sheetId="29" r:id="rId48"/>
-    <sheet name="Periclase" sheetId="30" r:id="rId49"/>
-    <sheet name="Quartz" sheetId="40" r:id="rId50"/>
-    <sheet name="Rutile" sheetId="41" r:id="rId51"/>
-    <sheet name="Andalusite" sheetId="42" r:id="rId52"/>
-    <sheet name="Kyanite" sheetId="43" r:id="rId53"/>
-    <sheet name="Sillimanite" sheetId="44" r:id="rId54"/>
-    <sheet name="Lime" sheetId="45" r:id="rId55"/>
-    <sheet name="Lawsonite" sheetId="46" r:id="rId56"/>
-    <sheet name="Zoisite" sheetId="47" r:id="rId57"/>
+    <sheet name="Feldspar_Pen" sheetId="59" r:id="rId12"/>
+    <sheet name="Feldspar(I1)" sheetId="12" r:id="rId13"/>
+    <sheet name="Feldspar(C1)" sheetId="11" r:id="rId14"/>
+    <sheet name="Brucite" sheetId="9" r:id="rId15"/>
+    <sheet name="Olivine(example)" sheetId="38" r:id="rId16"/>
+    <sheet name="Olivine" sheetId="2" r:id="rId17"/>
+    <sheet name="Olivine_Ori" sheetId="57" r:id="rId18"/>
+    <sheet name="Ilmenite" sheetId="13" r:id="rId19"/>
+    <sheet name="Fluid-H2O" sheetId="48" r:id="rId20"/>
+    <sheet name="Fluid-CO2-H2O" sheetId="1" r:id="rId21"/>
+    <sheet name="Fluid-NaCl-H2O" sheetId="34" r:id="rId22"/>
+    <sheet name="Fluid-NaCl-CO2-H2O" sheetId="35" r:id="rId23"/>
+    <sheet name="Orthopyroxene" sheetId="5" r:id="rId24"/>
+    <sheet name="Orthopyroxene_Ori" sheetId="56" r:id="rId25"/>
+    <sheet name="Garnet" sheetId="6" r:id="rId26"/>
+    <sheet name="Garnet_Ori" sheetId="54" r:id="rId27"/>
+    <sheet name="Clinopyroxene" sheetId="7" r:id="rId28"/>
+    <sheet name="Clinopyroxene_Ori" sheetId="55" r:id="rId29"/>
+    <sheet name="Spinel" sheetId="14" r:id="rId30"/>
+    <sheet name="Fluid(H18)" sheetId="15" r:id="rId31"/>
+    <sheet name="Fluid(H18)-NaCl-CO2" sheetId="36" r:id="rId32"/>
+    <sheet name="Amphibole" sheetId="16" r:id="rId33"/>
+    <sheet name="Biotite" sheetId="17" r:id="rId34"/>
+    <sheet name="Muscovite" sheetId="18" r:id="rId35"/>
+    <sheet name="Epidote" sheetId="19" r:id="rId36"/>
+    <sheet name="Cordierite" sheetId="20" r:id="rId37"/>
+    <sheet name="Chlorite" sheetId="21" r:id="rId38"/>
+    <sheet name="Staurolite" sheetId="22" r:id="rId39"/>
+    <sheet name="Chloritoid" sheetId="23" r:id="rId40"/>
+    <sheet name="Magnesite" sheetId="31" r:id="rId41"/>
+    <sheet name="Dolomite" sheetId="32" r:id="rId42"/>
+    <sheet name="Akimotoite" sheetId="24" r:id="rId43"/>
+    <sheet name="Corundum" sheetId="25" r:id="rId44"/>
+    <sheet name="Corundum_Ori" sheetId="58" r:id="rId45"/>
+    <sheet name="Perovskite" sheetId="26" r:id="rId46"/>
+    <sheet name="Ringwoodite" sheetId="27" r:id="rId47"/>
+    <sheet name="Wadsleyite" sheetId="28" r:id="rId48"/>
+    <sheet name="Majorite" sheetId="29" r:id="rId49"/>
+    <sheet name="Periclase" sheetId="30" r:id="rId50"/>
+    <sheet name="Quartz" sheetId="40" r:id="rId51"/>
+    <sheet name="Rutile" sheetId="41" r:id="rId52"/>
+    <sheet name="Andalusite" sheetId="42" r:id="rId53"/>
+    <sheet name="Kyanite" sheetId="43" r:id="rId54"/>
+    <sheet name="Sillimanite" sheetId="44" r:id="rId55"/>
+    <sheet name="Lime" sheetId="45" r:id="rId56"/>
+    <sheet name="Lawsonite" sheetId="46" r:id="rId57"/>
+    <sheet name="Zoisite" sheetId="47" r:id="rId58"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -90,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2535" uniqueCount="399">
   <si>
     <t>M0</t>
   </si>
@@ -1276,6 +1277,22 @@
   </si>
   <si>
     <t>Al</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>q,tc-ds633</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Si</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>q</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2545,6 +2562,621 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1D772E-180B-45A8-BBAB-4132C9AF2FBD}">
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" t="s">
+        <v>378</v>
+      </c>
+      <c r="F3" t="s">
+        <v>378</v>
+      </c>
+      <c r="G3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>395</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15">
+        <v>0.01</v>
+      </c>
+      <c r="C15">
+        <v>0.01</v>
+      </c>
+      <c r="D15">
+        <v>0.01</v>
+      </c>
+      <c r="E15">
+        <v>0.01</v>
+      </c>
+      <c r="F15">
+        <v>0.01</v>
+      </c>
+      <c r="G15">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>379</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>14600</v>
+      </c>
+      <c r="D19" s="2">
+        <v>24100</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="2">
+        <v>14600</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>48500</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="2">
+        <v>24100</v>
+      </c>
+      <c r="C21" s="2">
+        <v>48500</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>398</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>379</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>379</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>-9.35</v>
+      </c>
+      <c r="D25">
+        <v>-9.57</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26">
+        <v>-9.35</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27">
+        <v>-9.57</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>398</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>379</v>
+      </c>
+      <c r="C30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>379</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>-40</v>
+      </c>
+      <c r="D31" s="2">
+        <v>338</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32">
+        <v>-40</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>-130</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="2">
+        <v>338</v>
+      </c>
+      <c r="C33">
+        <v>-130</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>398</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
+        <v>379</v>
+      </c>
+      <c r="C36" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" t="s">
+        <v>91</v>
+      </c>
+      <c r="E36" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37">
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="C37">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>398</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15AA631E-41EF-4C75-90C8-4B3A68350948}">
   <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2935,7 +3567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FEBEB1C-7803-406E-B8B3-B5DE02E266CC}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3318,7 +3950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76BFBFBE-B733-46DB-BF97-8BF59558B35B}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3436,7 +4068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A55825-A6D1-4C0D-8BA7-1778913C2E99}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3681,7 +4313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA108C5-857B-4921-B88E-7848905E6592}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3906,22 +4538,22 @@
         <v>205</v>
       </c>
       <c r="B15">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="C15">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D15">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E15">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F15">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G15">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -4038,7 +4670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9D3FE9D-4C4E-439A-99E1-3B407EE76CAD}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -4362,7 +4994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD82132-BA46-451F-AE41-94B928E23AD4}">
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -4669,92 +5301,6 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B24" s="2"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA72E341-EE36-4FAC-B18C-398EE0AB5C1E}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>207</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12">
-        <v>6.7000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4922,6 +5468,92 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA72E341-EE36-4FAC-B18C-398EE0AB5C1E}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C88264-40FC-4B50-8522-4B84D7F1C1DD}">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -5185,7 +5817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE51046F-B358-4A85-B4E6-C1DD911090D9}">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -5448,7 +6080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C04816-4519-460B-9E4F-95C035B5C8B5}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -5610,7 +6242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C242AA7-14DE-4A41-B16E-9624765AFF4E}">
   <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6882,7 +7514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C134CBE1-05ED-4D46-B2ED-B315C22575A6}">
   <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -8325,7 +8957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9B45E6-FC06-4297-9961-A04532301994}">
   <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -8598,7 +9230,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -9099,7 +9731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2212AF05-99B1-4166-BE5E-DD3E604F7B4D}">
   <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -10073,7 +10705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C76E7016-9392-4505-861D-62BF353CCFF7}">
   <dimension ref="A1:P107"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -10725,43 +11357,43 @@
         <v>205</v>
       </c>
       <c r="B20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="K20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="M20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="N20">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -12221,7 +12853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93EEAFA-B82D-4052-B069-E45F44E9AD75}">
   <dimension ref="A1:P111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -14615,7 +15247,2913 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3ED75F-FEF6-4D60-971A-E4E781288CB0}">
+  <dimension ref="A1:S71"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O3" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>4</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>4</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>4</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>4</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>2</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>230</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>204</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>4</v>
+      </c>
+      <c r="N22">
+        <v>4</v>
+      </c>
+      <c r="O22">
+        <v>4</v>
+      </c>
+      <c r="P22">
+        <v>4</v>
+      </c>
+      <c r="Q22">
+        <v>4</v>
+      </c>
+      <c r="R22">
+        <v>1.75</v>
+      </c>
+      <c r="S22">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23">
+        <v>0.08</v>
+      </c>
+      <c r="C23">
+        <v>0.08</v>
+      </c>
+      <c r="D23">
+        <v>0.08</v>
+      </c>
+      <c r="E23">
+        <v>0.08</v>
+      </c>
+      <c r="F23">
+        <v>0.08</v>
+      </c>
+      <c r="G23">
+        <v>0.08</v>
+      </c>
+      <c r="H23">
+        <v>0.08</v>
+      </c>
+      <c r="I23">
+        <v>0.08</v>
+      </c>
+      <c r="J23">
+        <v>0.08</v>
+      </c>
+      <c r="K23">
+        <v>0.08</v>
+      </c>
+      <c r="L23">
+        <v>0.08</v>
+      </c>
+      <c r="M23">
+        <v>0.08</v>
+      </c>
+      <c r="N23">
+        <v>0.08</v>
+      </c>
+      <c r="O23">
+        <v>0.08</v>
+      </c>
+      <c r="P23">
+        <v>0.08</v>
+      </c>
+      <c r="Q23">
+        <v>0.08</v>
+      </c>
+      <c r="R23">
+        <v>0.08</v>
+      </c>
+      <c r="S23">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K26" t="s">
+        <v>48</v>
+      </c>
+      <c r="L26" t="s">
+        <v>49</v>
+      </c>
+      <c r="M26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>9500</v>
+      </c>
+      <c r="D27">
+        <v>-10300</v>
+      </c>
+      <c r="E27">
+        <v>-26500</v>
+      </c>
+      <c r="F27">
+        <v>-12000</v>
+      </c>
+      <c r="G27">
+        <v>-15100</v>
+      </c>
+      <c r="H27">
+        <v>20000</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>24600</v>
+      </c>
+      <c r="K27">
+        <v>-17800</v>
+      </c>
+      <c r="L27">
+        <v>-14600</v>
+      </c>
+      <c r="M27">
+        <v>17800</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28">
+        <v>9500</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>-26500</v>
+      </c>
+      <c r="E28">
+        <v>2200</v>
+      </c>
+      <c r="F28">
+        <v>2500</v>
+      </c>
+      <c r="G28">
+        <v>16800</v>
+      </c>
+      <c r="H28">
+        <v>-5000</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>15200</v>
+      </c>
+      <c r="K28">
+        <v>7000</v>
+      </c>
+      <c r="L28">
+        <v>4000</v>
+      </c>
+      <c r="M28">
+        <v>23700</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29">
+        <v>-10300</v>
+      </c>
+      <c r="C29">
+        <v>-26500</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>25500</v>
+      </c>
+      <c r="F29">
+        <v>14000</v>
+      </c>
+      <c r="G29">
+        <v>-1200</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>18000</v>
+      </c>
+      <c r="K29">
+        <v>-1100</v>
+      </c>
+      <c r="L29">
+        <v>9500</v>
+      </c>
+      <c r="M29">
+        <v>40300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30">
+        <v>-26500</v>
+      </c>
+      <c r="C30">
+        <v>2200</v>
+      </c>
+      <c r="D30">
+        <v>25500</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>18000</v>
+      </c>
+      <c r="G30">
+        <v>1500</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>7500</v>
+      </c>
+      <c r="K30">
+        <v>3000</v>
+      </c>
+      <c r="L30">
+        <v>-5600</v>
+      </c>
+      <c r="M30">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31">
+        <v>-12000</v>
+      </c>
+      <c r="C31">
+        <v>2500</v>
+      </c>
+      <c r="D31">
+        <v>14000</v>
+      </c>
+      <c r="E31">
+        <v>18000</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>7500</v>
+      </c>
+      <c r="H31">
+        <v>-30000</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6700</v>
+      </c>
+      <c r="K31">
+        <v>10000</v>
+      </c>
+      <c r="L31">
+        <v>-6500</v>
+      </c>
+      <c r="M31">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32">
+        <v>-15100</v>
+      </c>
+      <c r="C32">
+        <v>16800</v>
+      </c>
+      <c r="D32">
+        <v>-1200</v>
+      </c>
+      <c r="E32">
+        <v>1500</v>
+      </c>
+      <c r="F32">
+        <v>7500</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>10000</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>16500</v>
+      </c>
+      <c r="K32">
+        <v>-5900</v>
+      </c>
+      <c r="L32">
+        <v>7600</v>
+      </c>
+      <c r="M32">
+        <v>-8300</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33">
+        <v>20000</v>
+      </c>
+      <c r="C33">
+        <v>-5000</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>-30000</v>
+      </c>
+      <c r="G33">
+        <v>10000</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>10000</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35">
+        <v>24600</v>
+      </c>
+      <c r="C35">
+        <v>15200</v>
+      </c>
+      <c r="D35">
+        <v>18000</v>
+      </c>
+      <c r="E35">
+        <v>7500</v>
+      </c>
+      <c r="F35">
+        <v>6700</v>
+      </c>
+      <c r="G35">
+        <v>16500</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>9000</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36">
+        <v>-17800</v>
+      </c>
+      <c r="C36">
+        <v>7000</v>
+      </c>
+      <c r="D36">
+        <v>-1100</v>
+      </c>
+      <c r="E36">
+        <v>3000</v>
+      </c>
+      <c r="F36">
+        <v>10000</v>
+      </c>
+      <c r="G36">
+        <v>-5900</v>
+      </c>
+      <c r="H36">
+        <v>10000</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9000</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>-5600</v>
+      </c>
+      <c r="M36">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37">
+        <v>-14600</v>
+      </c>
+      <c r="C37">
+        <v>4000</v>
+      </c>
+      <c r="D37">
+        <v>9500</v>
+      </c>
+      <c r="E37">
+        <v>-5600</v>
+      </c>
+      <c r="F37">
+        <v>-6500</v>
+      </c>
+      <c r="G37">
+        <v>7600</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>-5600</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>17300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38">
+        <v>17800</v>
+      </c>
+      <c r="C38">
+        <v>23700</v>
+      </c>
+      <c r="D38">
+        <v>40300</v>
+      </c>
+      <c r="E38">
+        <v>9400</v>
+      </c>
+      <c r="F38">
+        <v>9200</v>
+      </c>
+      <c r="G38">
+        <v>-8300</v>
+      </c>
+      <c r="H38">
+        <v>60000</v>
+      </c>
+      <c r="I38">
+        <v>30000</v>
+      </c>
+      <c r="J38">
+        <v>30000</v>
+      </c>
+      <c r="K38">
+        <v>-100</v>
+      </c>
+      <c r="L38">
+        <v>17300</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" t="s">
+        <v>44</v>
+      </c>
+      <c r="H40" t="s">
+        <v>45</v>
+      </c>
+      <c r="I40" t="s">
+        <v>46</v>
+      </c>
+      <c r="J40" t="s">
+        <v>47</v>
+      </c>
+      <c r="K40" t="s">
+        <v>48</v>
+      </c>
+      <c r="L40" t="s">
+        <v>49</v>
+      </c>
+      <c r="M40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" t="s">
+        <v>43</v>
+      </c>
+      <c r="G54" t="s">
+        <v>44</v>
+      </c>
+      <c r="H54" t="s">
+        <v>45</v>
+      </c>
+      <c r="I54" t="s">
+        <v>46</v>
+      </c>
+      <c r="J54" t="s">
+        <v>47</v>
+      </c>
+      <c r="K54" t="s">
+        <v>48</v>
+      </c>
+      <c r="L54" t="s">
+        <v>49</v>
+      </c>
+      <c r="M54" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>-100</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>-3120</v>
+      </c>
+      <c r="F55">
+        <v>-550</v>
+      </c>
+      <c r="G55">
+        <v>-130</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>-50</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>-610</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56">
+        <v>-100</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>850</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>-40</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>-940</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>850</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>110</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>-860</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58">
+        <v>-3120</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>110</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>-1580</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59">
+        <v>-550</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>-50</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>-1580</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60">
+        <v>-130</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>-50</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>140</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>-660</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>-660</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>47</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>-40</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>140</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>48</v>
+      </c>
+      <c r="B64">
+        <v>-50</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>49</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>50</v>
+      </c>
+      <c r="B66">
+        <v>-610</v>
+      </c>
+      <c r="C66">
+        <v>-940</v>
+      </c>
+      <c r="D66">
+        <v>-860</v>
+      </c>
+      <c r="E66">
+        <v>-1580</v>
+      </c>
+      <c r="F66">
+        <v>-1580</v>
+      </c>
+      <c r="G66">
+        <v>-60</v>
+      </c>
+      <c r="H66">
+        <v>-660</v>
+      </c>
+      <c r="I66">
+        <v>-660</v>
+      </c>
+      <c r="J66">
+        <v>-600</v>
+      </c>
+      <c r="K66">
+        <v>220</v>
+      </c>
+      <c r="L66">
+        <v>50</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" t="s">
+        <v>40</v>
+      </c>
+      <c r="D68" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" t="s">
+        <v>43</v>
+      </c>
+      <c r="G68" t="s">
+        <v>44</v>
+      </c>
+      <c r="H68" t="s">
+        <v>45</v>
+      </c>
+      <c r="I68" t="s">
+        <v>46</v>
+      </c>
+      <c r="J68" t="s">
+        <v>47</v>
+      </c>
+      <c r="K68" t="s">
+        <v>48</v>
+      </c>
+      <c r="L68" t="s">
+        <v>49</v>
+      </c>
+      <c r="M68" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69">
+        <v>100</v>
+      </c>
+      <c r="C69">
+        <v>120</v>
+      </c>
+      <c r="D69">
+        <v>140</v>
+      </c>
+      <c r="E69">
+        <v>240</v>
+      </c>
+      <c r="F69">
+        <v>100</v>
+      </c>
+      <c r="G69">
+        <v>120</v>
+      </c>
+      <c r="H69">
+        <v>100</v>
+      </c>
+      <c r="I69">
+        <v>100</v>
+      </c>
+      <c r="J69">
+        <v>100</v>
+      </c>
+      <c r="K69">
+        <v>100</v>
+      </c>
+      <c r="L69">
+        <v>100</v>
+      </c>
+      <c r="M69">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>10</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC4BBFA-0045-4035-B334-91ED979C5005}">
   <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -15256,2913 +18794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3ED75F-FEF6-4D60-971A-E4E781288CB0}">
-  <dimension ref="A1:S71"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3" t="s">
-        <v>52</v>
-      </c>
-      <c r="O3" t="s">
-        <v>52</v>
-      </c>
-      <c r="P3" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" t="s">
-        <v>53</v>
-      </c>
-      <c r="S3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>221</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>222</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>4</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>4</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>223</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>4</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>4</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>224</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>226</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>228</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>229</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-      <c r="P16">
-        <v>1</v>
-      </c>
-      <c r="Q16">
-        <v>2</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>230</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <v>1</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="S19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>203</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>204</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>4</v>
-      </c>
-      <c r="N22">
-        <v>4</v>
-      </c>
-      <c r="O22">
-        <v>4</v>
-      </c>
-      <c r="P22">
-        <v>4</v>
-      </c>
-      <c r="Q22">
-        <v>4</v>
-      </c>
-      <c r="R22">
-        <v>1.75</v>
-      </c>
-      <c r="S22">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>205</v>
-      </c>
-      <c r="B23">
-        <v>0.08</v>
-      </c>
-      <c r="C23">
-        <v>0.08</v>
-      </c>
-      <c r="D23">
-        <v>0.08</v>
-      </c>
-      <c r="E23">
-        <v>0.08</v>
-      </c>
-      <c r="F23">
-        <v>0.08</v>
-      </c>
-      <c r="G23">
-        <v>0.08</v>
-      </c>
-      <c r="H23">
-        <v>0.08</v>
-      </c>
-      <c r="I23">
-        <v>0.08</v>
-      </c>
-      <c r="J23">
-        <v>0.08</v>
-      </c>
-      <c r="K23">
-        <v>0.08</v>
-      </c>
-      <c r="L23">
-        <v>0.08</v>
-      </c>
-      <c r="M23">
-        <v>0.08</v>
-      </c>
-      <c r="N23">
-        <v>0.08</v>
-      </c>
-      <c r="O23">
-        <v>0.08</v>
-      </c>
-      <c r="P23">
-        <v>0.08</v>
-      </c>
-      <c r="Q23">
-        <v>0.08</v>
-      </c>
-      <c r="R23">
-        <v>0.08</v>
-      </c>
-      <c r="S23">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>206</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J26" t="s">
-        <v>47</v>
-      </c>
-      <c r="K26" t="s">
-        <v>48</v>
-      </c>
-      <c r="L26" t="s">
-        <v>49</v>
-      </c>
-      <c r="M26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="C27">
-        <v>9500</v>
-      </c>
-      <c r="D27">
-        <v>-10300</v>
-      </c>
-      <c r="E27">
-        <v>-26500</v>
-      </c>
-      <c r="F27">
-        <v>-12000</v>
-      </c>
-      <c r="G27">
-        <v>-15100</v>
-      </c>
-      <c r="H27">
-        <v>20000</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>24600</v>
-      </c>
-      <c r="K27">
-        <v>-17800</v>
-      </c>
-      <c r="L27">
-        <v>-14600</v>
-      </c>
-      <c r="M27">
-        <v>17800</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28">
-        <v>9500</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>-26500</v>
-      </c>
-      <c r="E28">
-        <v>2200</v>
-      </c>
-      <c r="F28">
-        <v>2500</v>
-      </c>
-      <c r="G28">
-        <v>16800</v>
-      </c>
-      <c r="H28">
-        <v>-5000</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>15200</v>
-      </c>
-      <c r="K28">
-        <v>7000</v>
-      </c>
-      <c r="L28">
-        <v>4000</v>
-      </c>
-      <c r="M28">
-        <v>23700</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29">
-        <v>-10300</v>
-      </c>
-      <c r="C29">
-        <v>-26500</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>25500</v>
-      </c>
-      <c r="F29">
-        <v>14000</v>
-      </c>
-      <c r="G29">
-        <v>-1200</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>18000</v>
-      </c>
-      <c r="K29">
-        <v>-1100</v>
-      </c>
-      <c r="L29">
-        <v>9500</v>
-      </c>
-      <c r="M29">
-        <v>40300</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30">
-        <v>-26500</v>
-      </c>
-      <c r="C30">
-        <v>2200</v>
-      </c>
-      <c r="D30">
-        <v>25500</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>18000</v>
-      </c>
-      <c r="G30">
-        <v>1500</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>7500</v>
-      </c>
-      <c r="K30">
-        <v>3000</v>
-      </c>
-      <c r="L30">
-        <v>-5600</v>
-      </c>
-      <c r="M30">
-        <v>9400</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31">
-        <v>-12000</v>
-      </c>
-      <c r="C31">
-        <v>2500</v>
-      </c>
-      <c r="D31">
-        <v>14000</v>
-      </c>
-      <c r="E31">
-        <v>18000</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>7500</v>
-      </c>
-      <c r="H31">
-        <v>-30000</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>6700</v>
-      </c>
-      <c r="K31">
-        <v>10000</v>
-      </c>
-      <c r="L31">
-        <v>-6500</v>
-      </c>
-      <c r="M31">
-        <v>9200</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32">
-        <v>-15100</v>
-      </c>
-      <c r="C32">
-        <v>16800</v>
-      </c>
-      <c r="D32">
-        <v>-1200</v>
-      </c>
-      <c r="E32">
-        <v>1500</v>
-      </c>
-      <c r="F32">
-        <v>7500</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>10000</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>16500</v>
-      </c>
-      <c r="K32">
-        <v>-5900</v>
-      </c>
-      <c r="L32">
-        <v>7600</v>
-      </c>
-      <c r="M32">
-        <v>-8300</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33">
-        <v>20000</v>
-      </c>
-      <c r="C33">
-        <v>-5000</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>-30000</v>
-      </c>
-      <c r="G33">
-        <v>10000</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>10000</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35">
-        <v>24600</v>
-      </c>
-      <c r="C35">
-        <v>15200</v>
-      </c>
-      <c r="D35">
-        <v>18000</v>
-      </c>
-      <c r="E35">
-        <v>7500</v>
-      </c>
-      <c r="F35">
-        <v>6700</v>
-      </c>
-      <c r="G35">
-        <v>16500</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>9000</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36">
-        <v>-17800</v>
-      </c>
-      <c r="C36">
-        <v>7000</v>
-      </c>
-      <c r="D36">
-        <v>-1100</v>
-      </c>
-      <c r="E36">
-        <v>3000</v>
-      </c>
-      <c r="F36">
-        <v>10000</v>
-      </c>
-      <c r="G36">
-        <v>-5900</v>
-      </c>
-      <c r="H36">
-        <v>10000</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>9000</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>-5600</v>
-      </c>
-      <c r="M36">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37">
-        <v>-14600</v>
-      </c>
-      <c r="C37">
-        <v>4000</v>
-      </c>
-      <c r="D37">
-        <v>9500</v>
-      </c>
-      <c r="E37">
-        <v>-5600</v>
-      </c>
-      <c r="F37">
-        <v>-6500</v>
-      </c>
-      <c r="G37">
-        <v>7600</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>-5600</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>17300</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38">
-        <v>17800</v>
-      </c>
-      <c r="C38">
-        <v>23700</v>
-      </c>
-      <c r="D38">
-        <v>40300</v>
-      </c>
-      <c r="E38">
-        <v>9400</v>
-      </c>
-      <c r="F38">
-        <v>9200</v>
-      </c>
-      <c r="G38">
-        <v>-8300</v>
-      </c>
-      <c r="H38">
-        <v>60000</v>
-      </c>
-      <c r="I38">
-        <v>30000</v>
-      </c>
-      <c r="J38">
-        <v>30000</v>
-      </c>
-      <c r="K38">
-        <v>-100</v>
-      </c>
-      <c r="L38">
-        <v>17300</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" t="s">
-        <v>40</v>
-      </c>
-      <c r="D40" t="s">
-        <v>41</v>
-      </c>
-      <c r="E40" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" t="s">
-        <v>43</v>
-      </c>
-      <c r="G40" t="s">
-        <v>44</v>
-      </c>
-      <c r="H40" t="s">
-        <v>45</v>
-      </c>
-      <c r="I40" t="s">
-        <v>46</v>
-      </c>
-      <c r="J40" t="s">
-        <v>47</v>
-      </c>
-      <c r="K40" t="s">
-        <v>48</v>
-      </c>
-      <c r="L40" t="s">
-        <v>49</v>
-      </c>
-      <c r="M40" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" t="s">
-        <v>39</v>
-      </c>
-      <c r="C54" t="s">
-        <v>40</v>
-      </c>
-      <c r="D54" t="s">
-        <v>41</v>
-      </c>
-      <c r="E54" t="s">
-        <v>42</v>
-      </c>
-      <c r="F54" t="s">
-        <v>43</v>
-      </c>
-      <c r="G54" t="s">
-        <v>44</v>
-      </c>
-      <c r="H54" t="s">
-        <v>45</v>
-      </c>
-      <c r="I54" t="s">
-        <v>46</v>
-      </c>
-      <c r="J54" t="s">
-        <v>47</v>
-      </c>
-      <c r="K54" t="s">
-        <v>48</v>
-      </c>
-      <c r="L54" t="s">
-        <v>49</v>
-      </c>
-      <c r="M54" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
-        <v>-100</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-      <c r="E55">
-        <v>-3120</v>
-      </c>
-      <c r="F55">
-        <v>-550</v>
-      </c>
-      <c r="G55">
-        <v>-130</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>-50</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>-610</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56">
-        <v>-100</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>850</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
-        <v>-40</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>-940</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="C57">
-        <v>850</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57">
-        <v>110</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>-860</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58">
-        <v>-3120</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>110</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>0</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <v>-1580</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59">
-        <v>-550</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <v>-50</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59">
-        <v>-1580</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60">
-        <v>-130</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>-50</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>140</v>
-      </c>
-      <c r="K60">
-        <v>0</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>-660</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>46</v>
-      </c>
-      <c r="B62">
-        <v>0</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>-660</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>47</v>
-      </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="C63">
-        <v>-40</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
-      <c r="G63">
-        <v>140</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>-600</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>48</v>
-      </c>
-      <c r="B64">
-        <v>-50</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>49</v>
-      </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>50</v>
-      </c>
-      <c r="B66">
-        <v>-610</v>
-      </c>
-      <c r="C66">
-        <v>-940</v>
-      </c>
-      <c r="D66">
-        <v>-860</v>
-      </c>
-      <c r="E66">
-        <v>-1580</v>
-      </c>
-      <c r="F66">
-        <v>-1580</v>
-      </c>
-      <c r="G66">
-        <v>-60</v>
-      </c>
-      <c r="H66">
-        <v>-660</v>
-      </c>
-      <c r="I66">
-        <v>-660</v>
-      </c>
-      <c r="J66">
-        <v>-600</v>
-      </c>
-      <c r="K66">
-        <v>220</v>
-      </c>
-      <c r="L66">
-        <v>50</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>8</v>
-      </c>
-      <c r="B68" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" t="s">
-        <v>40</v>
-      </c>
-      <c r="D68" t="s">
-        <v>41</v>
-      </c>
-      <c r="E68" t="s">
-        <v>42</v>
-      </c>
-      <c r="F68" t="s">
-        <v>43</v>
-      </c>
-      <c r="G68" t="s">
-        <v>44</v>
-      </c>
-      <c r="H68" t="s">
-        <v>45</v>
-      </c>
-      <c r="I68" t="s">
-        <v>46</v>
-      </c>
-      <c r="J68" t="s">
-        <v>47</v>
-      </c>
-      <c r="K68" t="s">
-        <v>48</v>
-      </c>
-      <c r="L68" t="s">
-        <v>49</v>
-      </c>
-      <c r="M68" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B69">
-        <v>100</v>
-      </c>
-      <c r="C69">
-        <v>120</v>
-      </c>
-      <c r="D69">
-        <v>140</v>
-      </c>
-      <c r="E69">
-        <v>240</v>
-      </c>
-      <c r="F69">
-        <v>100</v>
-      </c>
-      <c r="G69">
-        <v>120</v>
-      </c>
-      <c r="H69">
-        <v>100</v>
-      </c>
-      <c r="I69">
-        <v>100</v>
-      </c>
-      <c r="J69">
-        <v>100</v>
-      </c>
-      <c r="K69">
-        <v>100</v>
-      </c>
-      <c r="L69">
-        <v>100</v>
-      </c>
-      <c r="M69">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>10</v>
-      </c>
-      <c r="B70">
-        <v>0</v>
-      </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>11</v>
-      </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9FEC348-0239-421D-8B87-57D917DDB388}">
   <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -20299,7 +20931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A34059C-F874-4CEA-B39C-6A118674F487}">
   <dimension ref="A1:O70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -23123,7 +23755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8134222-3A00-4FAC-A03C-B4190B949AC5}">
   <dimension ref="A1:S67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -25742,7 +26374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12D74A3-4D79-4402-83D3-64F73A88053B}">
   <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -26427,7 +27059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7C0D773-C514-4A73-9630-F36BE0FD5E2C}">
   <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -27478,7 +28110,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A790B61B-DAD7-426B-8DA0-753ADF78B32B}">
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -27752,7 +28384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8C8CA6A-F41A-453B-A5F7-CCB72E193EF9}">
   <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -28171,7 +28803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC82E37-876E-48F2-84B8-30B246AEC902}">
   <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -29124,7 +29756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EDDADE4-5183-47F0-B99E-63E7B7615289}">
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -29568,336 +30200,6 @@
         <v>30000</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32BD6C3E-36BD-4739-98A9-8BD7BBE5F83F}">
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B6">
-        <f>1/2</f>
-        <v>0.5</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B7">
-        <f>1/2</f>
-        <v>0.5</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>330</v>
-      </c>
-      <c r="B8">
-        <f>1/2</f>
-        <v>0.5</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>331</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <f>1/2</f>
-        <v>0.5</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>207</v>
-      </c>
-      <c r="B11">
-        <f>1/2</f>
-        <v>0.5</v>
-      </c>
-      <c r="C11">
-        <f>1/2</f>
-        <v>0.5</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>204</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>205</v>
-      </c>
-      <c r="B15">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="C15">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="D15">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="E15">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="F15">
-        <v>6.7000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>206</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C18" t="s">
-        <v>175</v>
-      </c>
-      <c r="D18" t="s">
-        <v>179</v>
-      </c>
-      <c r="E18" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2">
-        <v>4000</v>
-      </c>
-      <c r="D19" s="2">
-        <v>3000</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>175</v>
-      </c>
-      <c r="B20" s="2">
-        <v>4000</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20" s="2">
-        <v>3000</v>
-      </c>
-      <c r="E20" s="2">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>179</v>
-      </c>
-      <c r="B21" s="2">
-        <v>3000</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3000</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>176</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1000</v>
-      </c>
-      <c r="C22" s="2">
-        <v>5000</v>
-      </c>
-      <c r="D22" s="2">
-        <v>4000</v>
-      </c>
-      <c r="E22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -32459,6 +32761,336 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32BD6C3E-36BD-4739-98A9-8BD7BBE5F83F}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B6">
+        <f>1/2</f>
+        <v>0.5</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B7">
+        <f>1/2</f>
+        <v>0.5</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8">
+        <f>1/2</f>
+        <v>0.5</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f>1/2</f>
+        <v>0.5</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11">
+        <f>1/2</f>
+        <v>0.5</v>
+      </c>
+      <c r="C11">
+        <f>1/2</f>
+        <v>0.5</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="C15">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="D15">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="E15">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="F15">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" t="s">
+        <v>179</v>
+      </c>
+      <c r="E18" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>4000</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E20" s="2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B21" s="2">
+        <v>3000</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3000</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1000</v>
+      </c>
+      <c r="C22" s="2">
+        <v>5000</v>
+      </c>
+      <c r="D22" s="2">
+        <v>4000</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE21A17-0315-4C41-A263-479B78C65CAF}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -32609,7 +33241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE430B6-2E33-4DD9-8C16-0CD4C68F280F}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -32760,7 +33392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA0101F5-BC08-4CA4-A5EC-F868DB6B5E91}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -33035,7 +33667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533373C7-D62D-43FA-87F0-978DCF332C40}">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -33240,7 +33872,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE6E02DE-6641-407C-82D8-F2DB4581D3BA}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -33516,7 +34148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5127895C-0B42-4F4A-B39A-E3251A782B6D}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -33791,7 +34423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6519A2E7-F513-4EEE-B2DC-CB6841B4F69B}">
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -33947,7 +34579,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CC71AB-131B-4A07-8EE9-56F4B2ACA64B}">
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -34100,7 +34732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E835356-7737-4787-BBE4-4B0404DA114D}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -34455,161 +35087,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F54144DA-7F1C-4E32-88F3-EA4638CB97DB}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>351</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>352</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>204</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>205</v>
-      </c>
-      <c r="B13">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="C13">
-        <v>6.7000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>206</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" t="s">
-        <v>195</v>
-      </c>
-      <c r="C16" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>195</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>196</v>
-      </c>
-      <c r="B18" s="2">
-        <v>18000</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -34755,6 +35232,161 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F54144DA-7F1C-4E32-88F3-EA4638CB97DB}">
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="C13">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="2">
+        <v>18000</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{321402E3-4D4D-42ED-9150-AA32CD45A78A}">
   <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -34855,7 +35487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D97AAF0-136F-4218-9937-3E093AF27852}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -34938,7 +35570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5EBEFCF-D5CE-455E-84DF-BDB698A22590}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -35021,7 +35653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E540F2-4810-47FC-AB3B-97CD7B3657D9}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -35104,7 +35736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D73CB5A-16E4-4FCB-B19C-197DC8096D23}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -35187,7 +35819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5274FAD7-5388-4F55-99CF-0BBE7CD9D0AC}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -35270,7 +35902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD71DB1-A7FE-4AC4-8273-A64C4EA852E7}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -35353,7 +35985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5D766D-FFE3-41D6-9AE6-578A894AE2F7}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/Thermo/Solutions/solution_models_PFM.xlsx
+++ b/Thermo/Solutions/solution_models_PFM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\Thermo\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FDA618-B5DC-4825-BB24-F000E01542E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8AEFD7-B75F-4339-8356-D2ABC6E3056E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="8" activeTab="11" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" tabRatio="865" firstSheet="18" activeTab="27" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Melt (Ab-An)" sheetId="50" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2535" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2546" uniqueCount="402">
   <si>
     <t>M0</t>
   </si>
@@ -1293,6 +1293,18 @@
   </si>
   <si>
     <t>q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cor,tc-ds633</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cor</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2563,13 +2575,13 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1D772E-180B-45A8-BBAB-4132C9AF2FBD}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>201</v>
       </c>
@@ -2577,7 +2589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>202</v>
       </c>
@@ -2599,8 +2611,11 @@
       <c r="G3" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -2622,8 +2637,11 @@
       <c r="G4" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>380</v>
       </c>
@@ -2645,8 +2663,11 @@
       <c r="G6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>238</v>
       </c>
@@ -2668,8 +2689,11 @@
       <c r="G7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>239</v>
       </c>
@@ -2691,8 +2715,11 @@
       <c r="G8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>395</v>
       </c>
@@ -2714,459 +2741,643 @@
       <c r="G9">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>399</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>207</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>203</v>
       </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>204</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>205</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>0.01</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>0.01</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>0.01</v>
       </c>
-      <c r="E15">
+      <c r="E16">
         <v>0.01</v>
       </c>
-      <c r="F15">
+      <c r="F16">
         <v>0.01</v>
       </c>
-      <c r="G15">
+      <c r="G16">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="H16">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>206</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>5</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>379</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>94</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>91</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E19" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="F19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>379</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
         <v>14600</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D20" s="2">
         <v>24100</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B21" s="2">
         <v>14600</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
         <v>48500</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B22" s="2">
         <v>24100</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C22" s="2">
         <v>48500</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>398</v>
       </c>
-      <c r="B22" s="2">
-        <v>0</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>401</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>6</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B26" t="s">
         <v>379</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C26" t="s">
         <v>94</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D26" t="s">
         <v>91</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E26" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="F26" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>379</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
         <v>-9.35</v>
       </c>
-      <c r="D25">
+      <c r="D27">
         <v>-9.57</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>94</v>
       </c>
-      <c r="B26">
+      <c r="B28">
         <v>-9.35</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>91</v>
       </c>
-      <c r="B27">
+      <c r="B29">
         <v>-9.57</v>
       </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>398</v>
       </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>401</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>7</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B33" t="s">
         <v>379</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C33" t="s">
         <v>94</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D33" t="s">
         <v>91</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E33" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="F33" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>379</v>
       </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="C31">
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
         <v>-40</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D34" s="2">
         <v>338</v>
       </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>94</v>
       </c>
-      <c r="B32">
+      <c r="B35">
         <v>-40</v>
       </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
         <v>-130</v>
       </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B36" s="2">
         <v>338</v>
       </c>
-      <c r="C33">
+      <c r="C36">
         <v>-130</v>
       </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>398</v>
       </c>
-      <c r="B34" s="2">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>401</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>8</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B40" t="s">
         <v>379</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C40" t="s">
         <v>94</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D40" t="s">
         <v>91</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E40" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="F40" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>9</v>
       </c>
-      <c r="B37">
+      <c r="B41">
         <v>0.64700000000000002</v>
       </c>
-      <c r="C37">
+      <c r="C41">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>10</v>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>11</v>
       </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>398</v>
       </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40">
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>401</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
         <v>0</v>
       </c>
     </row>
@@ -11357,43 +11568,43 @@
         <v>205</v>
       </c>
       <c r="B20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="K20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="L20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N20">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">

--- a/Thermo/Solutions/solution_models_PFM.xlsx
+++ b/Thermo/Solutions/solution_models_PFM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\Thermo\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8AEFD7-B75F-4339-8356-D2ABC6E3056E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939F26D9-1A55-43F1-8C12-82C0E5F9C5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" tabRatio="865" firstSheet="18" activeTab="27" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" tabRatio="865" activeTab="1" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Melt (Ab-An)" sheetId="50" r:id="rId1"/>
@@ -4749,22 +4749,22 @@
         <v>205</v>
       </c>
       <c r="B15">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C15">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D15">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E15">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F15">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G15">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -7004,40 +7004,40 @@
         <v>205</v>
       </c>
       <c r="B19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="C19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="J19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="L19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="M19">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -11568,43 +11568,43 @@
         <v>205</v>
       </c>
       <c r="B20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="C20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="D20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="E20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="K20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="L20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="M20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="N20">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">

--- a/Thermo/Solutions/solution_models_PFM.xlsx
+++ b/Thermo/Solutions/solution_models_PFM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\Thermo\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939F26D9-1A55-43F1-8C12-82C0E5F9C5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9AF281-B156-4C21-A016-D68832D0C69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" tabRatio="865" activeTab="1" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="865" firstSheet="19" activeTab="23" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Melt (Ab-An)" sheetId="50" r:id="rId1"/>
@@ -7004,40 +7004,40 @@
         <v>205</v>
       </c>
       <c r="B19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="J19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="M19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -11568,43 +11568,43 @@
         <v>205</v>
       </c>
       <c r="B20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="D20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="E20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="F20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="G20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="H20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="I20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="J20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="K20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="L20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="M20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="N20">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
